--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74DAB7EB-F399-4C60-BA6D-F3AC1BDE95E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13890B4-78E3-4620-8094-FF1B1A73E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13890B4-78E3-4620-8094-FF1B1A73E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156DD60E-1822-466F-935F-E383ECAA3750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1702" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="109">
   <si>
     <t>C1</t>
   </si>
@@ -866,25 +866,25 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>177.03</c:v>
+                  <c:v>210.79</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>185.88150000000002</c:v>
+                  <c:v>221.3295</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>207.12509999999997</c:v>
+                  <c:v>246.62429999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>228.36870000000002</c:v>
+                  <c:v>271.91910000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>251.3826</c:v>
+                  <c:v>299.3218</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>281.47770000000003</c:v>
+                  <c:v>335.15609999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>306.26190000000003</c:v>
+                  <c:v>364.66669999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6272,7 +6272,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>177.03</v>
+        <v>210.79</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -6356,31 +6356,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>177.03</v>
+        <v>210.79</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>185.88150000000002</v>
+        <v>221.3295</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>207.12509999999997</v>
+        <v>246.62429999999998</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>228.36870000000002</v>
+        <v>271.91910000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>251.3826</v>
+        <v>299.3218</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>281.47770000000003</v>
+        <v>335.15609999999998</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>306.26190000000003</v>
+        <v>364.66669999999999</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -6583,31 +6583,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>65.501099999999994</v>
+        <v>77.9923</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>65.058525000000003</v>
+        <v>77.465324999999993</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>70.422533999999999</v>
+        <v>83.852261999999996</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>75.361671000000015</v>
+        <v>89.733303000000006</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>75.414779999999993</v>
+        <v>89.796539999999993</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>81.628533000000004</v>
+        <v>97.195268999999982</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>91.878570000000011</v>
+        <v>109.40000999999999</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -6650,31 +6650,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>104.4477</v>
+        <v>124.36609999999999</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>109.670085</v>
+        <v>130.584405</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>122.20380899999998</v>
+        <v>145.50833699999998</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>132.453846</v>
+        <v>157.713078</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>145.801908</v>
+        <v>173.60664399999999</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>157.62751200000002</v>
+        <v>187.68741600000001</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>165.38142600000003</v>
+        <v>196.920018</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -6717,31 +6717,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>5.3109000000000002</v>
+        <v>6.3236999999999997</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -6756,31 +6756,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>1.7702999999999918</v>
+        <v>2.1079000000000008</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>5.8419900000000098</v>
+        <v>6.9560699999999827</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>9.1878570000000082</v>
+        <v>10.940000999999995</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>15.242283000000015</v>
+        <v>18.14901900000001</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>24.855012000000016</v>
+        <v>29.594916000000012</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>36.910754999999995</v>
+        <v>43.949715000000026</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>43.691003999999964</v>
+        <v>52.022972000000038</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -6996,14 +6996,14 @@
     <row r="31" spans="2:24" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="L31" s="3">
         <f>SUMIFS(iea_data!H3:H9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)</f>
-        <v>-16.91</v>
+        <v>16.91</v>
       </c>
       <c r="N31" t="s">
         <v>33</v>
       </c>
       <c r="O31" s="3">
         <f>-1*L31</f>
-        <v>16.91</v>
+        <v>-16.91</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>
@@ -7524,7 +7524,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="10.59765625" customWidth="1"/>
@@ -7590,40 +7590,40 @@
         <v>98</v>
       </c>
       <c r="B11">
-        <v>2000</v>
+        <v>2015</v>
       </c>
       <c r="C11">
-        <v>75.849999999999994</v>
+        <v>58.76</v>
       </c>
       <c r="D11">
-        <v>53.54</v>
+        <v>75.23</v>
       </c>
       <c r="E11">
-        <v>4.3099999999999996</v>
+        <v>3.09</v>
       </c>
       <c r="F11">
         <v>0.02</v>
       </c>
       <c r="G11">
-        <v>3.29</v>
+        <v>14.46</v>
       </c>
       <c r="H11">
-        <v>-9.66</v>
+        <v>14.79</v>
       </c>
       <c r="I11">
-        <v>143.16999999999999</v>
+        <v>164.23</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>51.51</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>63.417000000000002</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>7.577</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.45">
@@ -7631,40 +7631,40 @@
         <v>98</v>
       </c>
       <c r="B12">
-        <v>2001</v>
+        <v>2016</v>
       </c>
       <c r="C12">
-        <v>74.36</v>
+        <v>61.61</v>
       </c>
       <c r="D12">
-        <v>55.12</v>
+        <v>78.34</v>
       </c>
       <c r="E12">
-        <v>4.2699999999999996</v>
+        <v>3.26</v>
       </c>
       <c r="F12">
         <v>0.02</v>
       </c>
       <c r="G12">
-        <v>4.3099999999999996</v>
+        <v>14.02</v>
       </c>
       <c r="H12">
-        <v>-11.04</v>
+        <v>12.02</v>
       </c>
       <c r="I12">
-        <v>143.72</v>
+        <v>166.1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>52.508000000000003</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>65.775999999999996</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>7.8079999999999998</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>57.968000000000004</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.45">
@@ -7672,40 +7672,40 @@
         <v>98</v>
       </c>
       <c r="B13">
-        <v>2002</v>
+        <v>2017</v>
       </c>
       <c r="C13">
-        <v>73.3</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="D13">
-        <v>54.71</v>
+        <v>77.92</v>
       </c>
       <c r="E13">
-        <v>4.29</v>
+        <v>3.3</v>
       </c>
       <c r="F13">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G13">
-        <v>4.47</v>
+        <v>13.27</v>
       </c>
       <c r="H13">
-        <v>-11.54</v>
+        <v>10.98</v>
       </c>
       <c r="I13">
-        <v>142.5</v>
+        <v>169.94</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>54.637999999999998</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>67.507000000000005</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>8.2490000000000006</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>59.258000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.45">
@@ -7713,40 +7713,40 @@
         <v>98</v>
       </c>
       <c r="B14">
-        <v>2003</v>
+        <v>2018</v>
       </c>
       <c r="C14">
-        <v>75.86</v>
+        <v>71.209999999999994</v>
       </c>
       <c r="D14">
-        <v>56.23</v>
+        <v>80.58</v>
       </c>
       <c r="E14">
-        <v>4.37</v>
+        <v>3.44</v>
       </c>
       <c r="F14">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G14">
-        <v>4.99</v>
+        <v>13.82</v>
       </c>
       <c r="H14">
-        <v>-15.15</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="I14">
-        <v>150.01</v>
+        <v>169.56</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>53.701000000000001</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>65.034000000000006</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>9.5869999999999997</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>55.447000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.45">
@@ -7754,40 +7754,40 @@
         <v>98</v>
       </c>
       <c r="B15">
-        <v>2004</v>
+        <v>2019</v>
       </c>
       <c r="C15">
-        <v>78.180000000000007</v>
+        <v>73.83</v>
       </c>
       <c r="D15">
-        <v>57.95</v>
+        <v>80.319999999999993</v>
       </c>
       <c r="E15">
-        <v>3.88</v>
+        <v>3.38</v>
       </c>
       <c r="F15">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="G15">
-        <v>5.31</v>
+        <v>17.87</v>
       </c>
       <c r="H15">
-        <v>-14.6</v>
+        <v>7.25</v>
       </c>
       <c r="I15">
-        <v>152.55000000000001</v>
+        <v>163.22</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>52.756999999999998</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>64.430000000000007</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>9.6519999999999992</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>54.777999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.45">
@@ -7795,40 +7795,40 @@
         <v>98</v>
       </c>
       <c r="B16">
-        <v>2005</v>
+        <v>2020</v>
       </c>
       <c r="C16">
-        <v>77.150000000000006</v>
+        <v>73.010000000000005</v>
       </c>
       <c r="D16">
-        <v>60.1</v>
+        <v>79.84</v>
       </c>
       <c r="E16">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="F16">
-        <v>0.02</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>20.62</v>
       </c>
       <c r="H16">
-        <v>-16.190000000000001</v>
+        <v>7.36</v>
       </c>
       <c r="I16">
-        <v>155.36000000000001</v>
+        <v>157.13</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>51.826999999999998</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>65.027000000000001</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>9.8190000000000008</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>55.207999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.45">
@@ -7836,40 +7836,40 @@
         <v>98</v>
       </c>
       <c r="B17">
-        <v>2006</v>
+        <v>2021</v>
       </c>
       <c r="C17">
-        <v>78.91</v>
+        <v>75.22</v>
       </c>
       <c r="D17">
-        <v>64.7</v>
+        <v>83.99</v>
       </c>
       <c r="E17">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="F17">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G17">
-        <v>4.79</v>
+        <v>15.1</v>
       </c>
       <c r="H17">
-        <v>-15.78</v>
+        <v>14.21</v>
       </c>
       <c r="I17">
-        <v>160.76</v>
+        <v>178.79</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>54.496000000000002</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>69.337999999999994</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>10.542</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>58.795999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.45">
@@ -7877,40 +7877,40 @@
         <v>98</v>
       </c>
       <c r="B18">
-        <v>2007</v>
+        <v>2022</v>
       </c>
       <c r="C18">
-        <v>82.1</v>
+        <v>75.180000000000007</v>
       </c>
       <c r="D18">
-        <v>65.06</v>
+        <v>83.17</v>
       </c>
       <c r="E18">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="F18">
-        <v>0.02</v>
+        <v>0.17</v>
       </c>
       <c r="G18">
-        <v>7.76</v>
+        <v>15.24</v>
       </c>
       <c r="H18">
-        <v>-13.11</v>
+        <v>16.91</v>
       </c>
       <c r="I18">
-        <v>158.76</v>
+        <v>178.64</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>50.323999999999998</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>65.281999999999996</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>9.7690000000000001</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>55.512999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.45">
@@ -7918,40 +7918,40 @@
         <v>98</v>
       </c>
       <c r="B19">
-        <v>2008</v>
+        <v>2023</v>
       </c>
       <c r="C19">
-        <v>78.39</v>
+        <v>76.92</v>
       </c>
       <c r="D19">
-        <v>69.83</v>
+        <v>79.83</v>
       </c>
       <c r="E19">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="F19">
-        <v>0.02</v>
+        <v>0.23</v>
       </c>
       <c r="G19">
-        <v>9.0299999999999994</v>
+        <v>15.14</v>
       </c>
       <c r="H19">
-        <v>-9.6999999999999993</v>
+        <v>11.4</v>
       </c>
       <c r="I19">
-        <v>154.71</v>
+        <v>165.99</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>49.042999999999999</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>60.381</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>8.3460000000000001</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>52.034999999999997</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.45">
@@ -7959,573 +7959,40 @@
         <v>98</v>
       </c>
       <c r="B20">
-        <v>2009</v>
+        <v>2024</v>
       </c>
       <c r="C20">
-        <v>73.959999999999994</v>
+        <v>84.11</v>
       </c>
       <c r="D20">
-        <v>69.69</v>
+        <v>82.19</v>
       </c>
       <c r="E20">
-        <v>2.86</v>
+        <v>3.57</v>
       </c>
       <c r="F20">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="G20">
-        <v>7.4</v>
+        <v>15.21</v>
       </c>
       <c r="H20">
-        <v>-9.59</v>
+        <v>13.25</v>
       </c>
       <c r="I20">
-        <v>151.12</v>
+        <v>171.32</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>47.503</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>57.613999999999997</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>8.0820000000000007</v>
       </c>
       <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>98</v>
-      </c>
-      <c r="B21">
-        <v>2010</v>
-      </c>
-      <c r="C21">
-        <v>76.11</v>
-      </c>
-      <c r="D21">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="E21">
-        <v>2.96</v>
-      </c>
-      <c r="F21">
-        <v>0.02</v>
-      </c>
-      <c r="G21">
-        <v>6.31</v>
-      </c>
-      <c r="H21">
-        <v>-7.66</v>
-      </c>
-      <c r="I21">
-        <v>157.09</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>98</v>
-      </c>
-      <c r="B22">
-        <v>2011</v>
-      </c>
-      <c r="C22">
-        <v>78.38</v>
-      </c>
-      <c r="D22">
-        <v>74.040000000000006</v>
-      </c>
-      <c r="E22">
-        <v>2.96</v>
-      </c>
-      <c r="F22">
-        <v>0.02</v>
-      </c>
-      <c r="G22">
-        <v>6.78</v>
-      </c>
-      <c r="H22">
-        <v>-12.02</v>
-      </c>
-      <c r="I22">
-        <v>163.12</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>98</v>
-      </c>
-      <c r="B23">
-        <v>2012</v>
-      </c>
-      <c r="C23">
-        <v>79.09</v>
-      </c>
-      <c r="D23">
-        <v>74.260000000000005</v>
-      </c>
-      <c r="E23">
-        <v>2.87</v>
-      </c>
-      <c r="F23">
-        <v>0.02</v>
-      </c>
-      <c r="G23">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="H23">
-        <v>-12.64</v>
-      </c>
-      <c r="I23">
-        <v>161.71</v>
-      </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>98</v>
-      </c>
-      <c r="B24">
-        <v>2013</v>
-      </c>
-      <c r="C24">
-        <v>80.930000000000007</v>
-      </c>
-      <c r="D24">
-        <v>73.11</v>
-      </c>
-      <c r="E24">
-        <v>2.85</v>
-      </c>
-      <c r="F24">
-        <v>0.02</v>
-      </c>
-      <c r="G24">
-        <v>7.8</v>
-      </c>
-      <c r="H24">
-        <v>-12.32</v>
-      </c>
-      <c r="I24">
-        <v>164.02</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25">
-        <v>2014</v>
-      </c>
-      <c r="C25">
-        <v>80.56</v>
-      </c>
-      <c r="D25">
-        <v>74.75</v>
-      </c>
-      <c r="E25">
-        <v>2.7</v>
-      </c>
-      <c r="F25">
-        <v>0.02</v>
-      </c>
-      <c r="G25">
-        <v>13.51</v>
-      </c>
-      <c r="H25">
-        <v>-11.34</v>
-      </c>
-      <c r="I25">
-        <v>158.51</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26">
-        <v>2015</v>
-      </c>
-      <c r="C26">
-        <v>82.98</v>
-      </c>
-      <c r="D26">
-        <v>75.23</v>
-      </c>
-      <c r="E26">
-        <v>2.8</v>
-      </c>
-      <c r="F26">
-        <v>0.02</v>
-      </c>
-      <c r="G26">
-        <v>14.46</v>
-      </c>
-      <c r="H26">
-        <v>-14.79</v>
-      </c>
-      <c r="I26">
-        <v>164.34</v>
-      </c>
-      <c r="J26">
-        <v>51.51</v>
-      </c>
-      <c r="K26">
-        <v>63.417000000000002</v>
-      </c>
-      <c r="L26">
-        <v>7.577</v>
-      </c>
-      <c r="M26">
-        <v>55.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27">
-        <v>2016</v>
-      </c>
-      <c r="C27">
-        <v>84</v>
-      </c>
-      <c r="D27">
-        <v>78.34</v>
-      </c>
-      <c r="E27">
-        <v>2.96</v>
-      </c>
-      <c r="F27">
-        <v>0.02</v>
-      </c>
-      <c r="G27">
-        <v>14.02</v>
-      </c>
-      <c r="H27">
-        <v>-12.02</v>
-      </c>
-      <c r="I27">
-        <v>166.15</v>
-      </c>
-      <c r="J27">
-        <v>52.508000000000003</v>
-      </c>
-      <c r="K27">
-        <v>65.775999999999996</v>
-      </c>
-      <c r="L27">
-        <v>7.8079999999999998</v>
-      </c>
-      <c r="M27">
-        <v>57.968000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28">
-        <v>2017</v>
-      </c>
-      <c r="C28">
-        <v>88.21</v>
-      </c>
-      <c r="D28">
-        <v>77.91</v>
-      </c>
-      <c r="E28">
-        <v>3.06</v>
-      </c>
-      <c r="F28">
-        <v>0.03</v>
-      </c>
-      <c r="G28">
-        <v>13.27</v>
-      </c>
-      <c r="H28">
-        <v>-10.98</v>
-      </c>
-      <c r="I28">
-        <v>169.99</v>
-      </c>
-      <c r="J28">
-        <v>54.637999999999998</v>
-      </c>
-      <c r="K28">
-        <v>67.507000000000005</v>
-      </c>
-      <c r="L28">
-        <v>8.2490000000000006</v>
-      </c>
-      <c r="M28">
-        <v>59.258000000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>98</v>
-      </c>
-      <c r="B29">
-        <v>2018</v>
-      </c>
-      <c r="C29">
-        <v>88.27</v>
-      </c>
-      <c r="D29">
-        <v>80.569999999999993</v>
-      </c>
-      <c r="E29">
-        <v>3.2</v>
-      </c>
-      <c r="F29">
-        <v>0.03</v>
-      </c>
-      <c r="G29">
-        <v>13.82</v>
-      </c>
-      <c r="H29">
-        <v>-8.1199999999999992</v>
-      </c>
-      <c r="I29">
-        <v>169.62</v>
-      </c>
-      <c r="J29">
-        <v>53.701000000000001</v>
-      </c>
-      <c r="K29">
-        <v>65.034000000000006</v>
-      </c>
-      <c r="L29">
-        <v>9.5869999999999997</v>
-      </c>
-      <c r="M29">
-        <v>55.447000000000003</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30">
-        <v>2019</v>
-      </c>
-      <c r="C30">
-        <v>86.39</v>
-      </c>
-      <c r="D30">
-        <v>80.31</v>
-      </c>
-      <c r="E30">
-        <v>3.15</v>
-      </c>
-      <c r="F30">
-        <v>0.03</v>
-      </c>
-      <c r="G30">
-        <v>17.87</v>
-      </c>
-      <c r="H30">
-        <v>-7.25</v>
-      </c>
-      <c r="I30">
-        <v>163.28</v>
-      </c>
-      <c r="J30">
-        <v>52.756999999999998</v>
-      </c>
-      <c r="K30">
-        <v>64.430000000000007</v>
-      </c>
-      <c r="L30">
-        <v>9.6519999999999992</v>
-      </c>
-      <c r="M30">
-        <v>54.777999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31">
-        <v>2020</v>
-      </c>
-      <c r="C31">
-        <v>84.93</v>
-      </c>
-      <c r="D31">
-        <v>78.86</v>
-      </c>
-      <c r="E31">
-        <v>2.89</v>
-      </c>
-      <c r="F31">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G31">
-        <v>20.62</v>
-      </c>
-      <c r="H31">
-        <v>-7.36</v>
-      </c>
-      <c r="I31">
-        <v>157.22</v>
-      </c>
-      <c r="J31">
-        <v>51.826999999999998</v>
-      </c>
-      <c r="K31">
-        <v>65.027000000000001</v>
-      </c>
-      <c r="L31">
-        <v>9.8190000000000008</v>
-      </c>
-      <c r="M31">
-        <v>55.207999999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32">
-        <v>2021</v>
-      </c>
-      <c r="C32">
-        <v>87.3</v>
-      </c>
-      <c r="D32">
-        <v>83.98</v>
-      </c>
-      <c r="E32">
-        <v>3.22</v>
-      </c>
-      <c r="F32">
-        <v>0.06</v>
-      </c>
-      <c r="G32">
-        <v>15.1</v>
-      </c>
-      <c r="H32">
-        <v>-14.21</v>
-      </c>
-      <c r="I32">
-        <v>178.87</v>
-      </c>
-      <c r="J32">
-        <v>54.496000000000002</v>
-      </c>
-      <c r="K32">
-        <v>69.337999999999994</v>
-      </c>
-      <c r="L32">
-        <v>10.542</v>
-      </c>
-      <c r="M32">
-        <v>58.795999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33">
-        <v>2022</v>
-      </c>
-      <c r="C33">
-        <v>83.2</v>
-      </c>
-      <c r="D33">
-        <v>84.78</v>
-      </c>
-      <c r="E33">
-        <v>3.32</v>
-      </c>
-      <c r="F33">
-        <v>0.17</v>
-      </c>
-      <c r="G33">
-        <v>15.24</v>
-      </c>
-      <c r="H33">
-        <v>-16.91</v>
-      </c>
-      <c r="I33">
-        <v>178.7</v>
-      </c>
-      <c r="J33">
-        <v>50.323999999999998</v>
-      </c>
-      <c r="K33">
-        <v>65.281999999999996</v>
-      </c>
-      <c r="L33">
-        <v>9.7690000000000001</v>
-      </c>
-      <c r="M33">
-        <v>55.512999999999998</v>
+        <v>49.531999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156DD60E-1822-466F-935F-E383ECAA3750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF850BF9-5FEA-435A-B739-13E228B4DD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF850BF9-5FEA-435A-B739-13E228B4DD3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861344CA-FF84-46B1-822C-EBC0B2507607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{861344CA-FF84-46B1-822C-EBC0B2507607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA734A05-C76C-4E6F-964F-28B54A66BA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -866,25 +866,25 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>210.79</c:v>
+                  <c:v>176.97</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>221.3295</c:v>
+                  <c:v>185.8185</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>246.62429999999998</c:v>
+                  <c:v>207.05489999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>271.91910000000001</c:v>
+                  <c:v>228.29130000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>299.3218</c:v>
+                  <c:v>251.29739999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>335.15609999999998</c:v>
+                  <c:v>281.38229999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>364.66669999999999</c:v>
+                  <c:v>306.15809999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6272,7 +6272,7 @@
     <row r="11" spans="1:34" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="N11" s="17">
         <f>SUMIFS(iea_data!I3:I9999,iea_data!$B$3:$B$9999,$N$10,iea_data!$A$3:A$9999,$A$1)+O30-O31</f>
-        <v>210.79</v>
+        <v>176.97</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>55</v>
@@ -6356,31 +6356,31 @@
       </c>
       <c r="O15" s="8">
         <f>N11</f>
-        <v>210.79</v>
+        <v>176.97</v>
       </c>
       <c r="P15" s="8">
         <f t="shared" ref="P15:U15" si="0">$N$11*E15</f>
-        <v>221.3295</v>
+        <v>185.8185</v>
       </c>
       <c r="Q15" s="8">
         <f t="shared" si="0"/>
-        <v>246.62429999999998</v>
+        <v>207.05489999999998</v>
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>271.91910000000001</v>
+        <v>228.29130000000001</v>
       </c>
       <c r="S15" s="8">
         <f t="shared" si="0"/>
-        <v>299.3218</v>
+        <v>251.29739999999998</v>
       </c>
       <c r="T15" s="8">
         <f t="shared" si="0"/>
-        <v>335.15609999999998</v>
+        <v>281.38229999999999</v>
       </c>
       <c r="U15" s="8">
         <f t="shared" si="0"/>
-        <v>364.66669999999999</v>
+        <v>306.15809999999999</v>
       </c>
     </row>
     <row r="16" spans="1:34" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
@@ -6583,31 +6583,31 @@
       </c>
       <c r="O20" s="6">
         <f t="shared" si="2"/>
-        <v>77.9923</v>
+        <v>65.478899999999996</v>
       </c>
       <c r="P20" s="6">
         <f t="shared" si="2"/>
-        <v>77.465324999999993</v>
+        <v>65.036474999999996</v>
       </c>
       <c r="Q20" s="6">
         <f t="shared" si="2"/>
-        <v>83.852261999999996</v>
+        <v>70.398665999999992</v>
       </c>
       <c r="R20" s="6">
         <f t="shared" si="2"/>
-        <v>89.733303000000006</v>
+        <v>75.336129</v>
       </c>
       <c r="S20" s="6">
         <f t="shared" si="2"/>
-        <v>89.796539999999993</v>
+        <v>75.389219999999995</v>
       </c>
       <c r="T20" s="6">
         <f t="shared" si="2"/>
-        <v>97.195268999999982</v>
+        <v>81.600866999999994</v>
       </c>
       <c r="U20" s="6">
         <f t="shared" si="2"/>
-        <v>109.40000999999999</v>
+        <v>91.847429999999989</v>
       </c>
       <c r="V20" t="s">
         <v>16</v>
@@ -6650,31 +6650,31 @@
       </c>
       <c r="O21" s="6">
         <f t="shared" si="2"/>
-        <v>124.36609999999999</v>
+        <v>104.41229999999999</v>
       </c>
       <c r="P21" s="6">
         <f t="shared" si="2"/>
-        <v>130.584405</v>
+        <v>109.632915</v>
       </c>
       <c r="Q21" s="6">
         <f t="shared" si="2"/>
-        <v>145.50833699999998</v>
+        <v>122.16239099999999</v>
       </c>
       <c r="R21" s="6">
         <f t="shared" si="2"/>
-        <v>157.713078</v>
+        <v>132.40895399999999</v>
       </c>
       <c r="S21" s="6">
         <f t="shared" si="2"/>
-        <v>173.60664399999999</v>
+        <v>145.75249199999999</v>
       </c>
       <c r="T21" s="6">
         <f t="shared" si="2"/>
-        <v>187.68741600000001</v>
+        <v>157.57408800000002</v>
       </c>
       <c r="U21" s="6">
         <f t="shared" si="2"/>
-        <v>196.920018</v>
+        <v>165.32537400000001</v>
       </c>
       <c r="V21" t="s">
         <v>16</v>
@@ -6717,31 +6717,31 @@
       </c>
       <c r="O22" s="6">
         <f>D22*O$15</f>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="P22" s="6">
         <f t="shared" ref="P22:U22" si="3">O22</f>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="Q22" s="6">
         <f t="shared" si="3"/>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="R22" s="6">
         <f t="shared" si="3"/>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="S22" s="6">
         <f t="shared" si="3"/>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="T22" s="6">
         <f t="shared" si="3"/>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="U22" s="6">
         <f t="shared" si="3"/>
-        <v>6.3236999999999997</v>
+        <v>5.3090999999999999</v>
       </c>
       <c r="V22" t="s">
         <v>16</v>
@@ -6756,31 +6756,31 @@
       </c>
       <c r="O23" s="6">
         <f t="shared" ref="O23:U23" si="4">O15-SUM(O20:O22)</f>
-        <v>2.1079000000000008</v>
+        <v>1.7697000000000287</v>
       </c>
       <c r="P23" s="6">
         <f t="shared" si="4"/>
-        <v>6.9560699999999827</v>
+        <v>5.8400100000000066</v>
       </c>
       <c r="Q23" s="6">
         <f t="shared" si="4"/>
-        <v>10.940000999999995</v>
+        <v>9.1847429999999974</v>
       </c>
       <c r="R23" s="6">
         <f t="shared" si="4"/>
-        <v>18.14901900000001</v>
+        <v>15.237117000000012</v>
       </c>
       <c r="S23" s="6">
         <f t="shared" si="4"/>
-        <v>29.594916000000012</v>
+        <v>24.846587999999997</v>
       </c>
       <c r="T23" s="6">
         <f t="shared" si="4"/>
-        <v>43.949715000000026</v>
+        <v>36.898244999999974</v>
       </c>
       <c r="U23" s="6">
         <f t="shared" si="4"/>
-        <v>52.022972000000038</v>
+        <v>43.676196000000004</v>
       </c>
       <c r="V23" t="s">
         <v>16</v>
@@ -7002,8 +7002,8 @@
         <v>33</v>
       </c>
       <c r="O31" s="3">
-        <f>-1*L31</f>
-        <v>-16.91</v>
+        <f>ABS(L31)</f>
+        <v>16.91</v>
       </c>
       <c r="Q31" s="6"/>
       <c r="R31" s="6"/>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA734A05-C76C-4E6F-964F-28B54A66BA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAB6DA0-BDAB-4816-8077-B0A7BCB32327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEAB6DA0-BDAB-4816-8077-B0A7BCB32327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24751D49-D9DE-42E6-83AC-FB8046B5B1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24751D49-D9DE-42E6-83AC-FB8046B5B1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2CC02A-D4D9-4873-9F55-C7843F53FB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2CC02A-D4D9-4873-9F55-C7843F53FB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBF2854-CE36-4334-8C59-DE0695124BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBF2854-CE36-4334-8C59-DE0695124BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35A267C-542A-489D-AA3D-3549D2D18D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35A267C-542A-489D-AA3D-3549D2D18D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B41E53E-7D54-4061-BD7C-88AA4D311A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B41E53E-7D54-4061-BD7C-88AA4D311A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376C23E4-2B3C-4C6B-8DAA-F031E6E02659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376C23E4-2B3C-4C6B-8DAA-F031E6E02659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB42E6A0-F271-4F21-916A-7657AEAB3C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB42E6A0-F271-4F21-916A-7657AEAB3C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E64ED7-1979-4320-AA9C-58B095007274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10E64ED7-1979-4320-AA9C-58B095007274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582844F7-F611-4649-957D-029AE37D5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -418,21 +418,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -441,7 +441,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -449,7 +449,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -457,7 +457,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -465,21 +465,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +492,7 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +512,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5605,39 +5605,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5689,7 +5689,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5800,6 +5800,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -5808,13 +5815,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5879,31 +5879,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6416,7 +6396,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -6924,7 +6904,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -7155,7 +7135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
         <v>~TFM_INS-TS: region=POL; attribute=flo_cost;pset_pn=-IMP*Z</v>
@@ -18160,8 +18140,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257" t="e">
-        <v>#NUM!</v>
+      <c r="E257">
+        <v>65535</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -18169,8 +18149,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257" t="e">
-        <v>#NUM!</v>
+      <c r="I257">
+        <v>65535</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -18198,8 +18178,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258" t="e">
-        <v>#NUM!</v>
+      <c r="E258">
+        <v>65535</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -18207,8 +18187,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258" t="e">
-        <v>#NUM!</v>
+      <c r="I258">
+        <v>65535</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -18236,8 +18216,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259" t="e">
-        <v>#NUM!</v>
+      <c r="E259">
+        <v>65535</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -18245,8 +18225,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259" t="e">
-        <v>#NUM!</v>
+      <c r="I259">
+        <v>65535</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -18274,8 +18254,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260" t="e">
-        <v>#NUM!</v>
+      <c r="E260">
+        <v>65535</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -18283,8 +18263,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260" t="e">
-        <v>#NUM!</v>
+      <c r="I260">
+        <v>65535</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -18312,8 +18292,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261" t="e">
-        <v>#NUM!</v>
+      <c r="E261">
+        <v>65535</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -18321,8 +18301,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261" t="e">
-        <v>#NUM!</v>
+      <c r="I261">
+        <v>65535</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -18350,8 +18330,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262" t="e">
-        <v>#NUM!</v>
+      <c r="E262">
+        <v>65535</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -18359,8 +18339,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262" t="e">
-        <v>#NUM!</v>
+      <c r="I262">
+        <v>65535</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -18429,8 +18409,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264" t="e">
-        <v>#NUM!</v>
+      <c r="E264">
+        <v>65535</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -18438,8 +18418,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264" t="e">
-        <v>#NUM!</v>
+      <c r="I264">
+        <v>65535</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -18467,8 +18447,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265" t="e">
-        <v>#NUM!</v>
+      <c r="E265">
+        <v>65535</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -18476,8 +18456,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265" t="e">
-        <v>#NUM!</v>
+      <c r="I265">
+        <v>65535</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -18505,8 +18485,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266" t="e">
-        <v>#NUM!</v>
+      <c r="E266">
+        <v>65535</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -18514,8 +18494,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266" t="e">
-        <v>#NUM!</v>
+      <c r="I266">
+        <v>65535</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -18543,8 +18523,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267" t="e">
-        <v>#NUM!</v>
+      <c r="E267">
+        <v>65535</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -18552,8 +18532,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267" t="e">
-        <v>#NUM!</v>
+      <c r="I267">
+        <v>65535</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -18581,8 +18561,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268" t="e">
-        <v>#NUM!</v>
+      <c r="E268">
+        <v>65535</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -18590,8 +18570,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268" t="e">
-        <v>#NUM!</v>
+      <c r="I268">
+        <v>65535</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -18619,8 +18599,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269" t="e">
-        <v>#NUM!</v>
+      <c r="E269">
+        <v>65535</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -18628,8 +18608,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269" t="e">
-        <v>#NUM!</v>
+      <c r="I269">
+        <v>65535</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -18698,8 +18678,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271" t="e">
-        <v>#NUM!</v>
+      <c r="E271">
+        <v>65535</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -18707,8 +18687,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271" t="e">
-        <v>#NUM!</v>
+      <c r="I271">
+        <v>65535</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -18736,8 +18716,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272" t="e">
-        <v>#NUM!</v>
+      <c r="E272">
+        <v>65535</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -18745,8 +18725,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272" t="e">
-        <v>#NUM!</v>
+      <c r="I272">
+        <v>65535</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -18774,8 +18754,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273" t="e">
-        <v>#NUM!</v>
+      <c r="E273">
+        <v>65535</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -18783,8 +18763,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273" t="e">
-        <v>#NUM!</v>
+      <c r="I273">
+        <v>65535</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -18812,8 +18792,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274" t="e">
-        <v>#NUM!</v>
+      <c r="E274">
+        <v>65535</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -18821,8 +18801,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274" t="e">
-        <v>#NUM!</v>
+      <c r="I274">
+        <v>65535</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -18850,8 +18830,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275" t="e">
-        <v>#NUM!</v>
+      <c r="E275">
+        <v>65535</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -18859,8 +18839,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275" t="e">
-        <v>#NUM!</v>
+      <c r="I275">
+        <v>65535</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -18888,8 +18868,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276" t="e">
-        <v>#NUM!</v>
+      <c r="E276">
+        <v>65535</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -18897,8 +18877,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276" t="e">
-        <v>#NUM!</v>
+      <c r="I276">
+        <v>65535</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -19541,8 +19521,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292" t="e">
-        <v>#NUM!</v>
+      <c r="E292">
+        <v>65535</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -19550,8 +19530,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292" t="e">
-        <v>#NUM!</v>
+      <c r="I292">
+        <v>65535</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -19579,8 +19559,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293" t="e">
-        <v>#NUM!</v>
+      <c r="E293">
+        <v>65535</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -19588,8 +19568,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293" t="e">
-        <v>#NUM!</v>
+      <c r="I293">
+        <v>65535</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -19617,8 +19597,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294" t="e">
-        <v>#NUM!</v>
+      <c r="E294">
+        <v>65535</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -19626,8 +19606,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294" t="e">
-        <v>#NUM!</v>
+      <c r="I294">
+        <v>65535</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -19655,8 +19635,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295" t="e">
-        <v>#NUM!</v>
+      <c r="E295">
+        <v>65535</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -19664,8 +19644,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295" t="e">
-        <v>#NUM!</v>
+      <c r="I295">
+        <v>65535</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -19693,8 +19673,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296" t="e">
-        <v>#NUM!</v>
+      <c r="E296">
+        <v>65535</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -19702,8 +19682,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296" t="e">
-        <v>#NUM!</v>
+      <c r="I296">
+        <v>65535</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -19731,8 +19711,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297" t="e">
-        <v>#NUM!</v>
+      <c r="E297">
+        <v>65535</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -19740,8 +19720,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297" t="e">
-        <v>#NUM!</v>
+      <c r="I297">
+        <v>65535</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -19810,8 +19790,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299" t="e">
-        <v>#NUM!</v>
+      <c r="E299">
+        <v>65535</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -19819,8 +19799,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299" t="e">
-        <v>#NUM!</v>
+      <c r="I299">
+        <v>65535</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -19848,8 +19828,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300" t="e">
-        <v>#NUM!</v>
+      <c r="E300">
+        <v>65535</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -19857,8 +19837,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300" t="e">
-        <v>#NUM!</v>
+      <c r="I300">
+        <v>65535</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -19886,8 +19866,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301" t="e">
-        <v>#NUM!</v>
+      <c r="E301">
+        <v>65535</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -19895,8 +19875,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301" t="e">
-        <v>#NUM!</v>
+      <c r="I301">
+        <v>65535</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -19924,8 +19904,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302" t="e">
-        <v>#NUM!</v>
+      <c r="E302">
+        <v>65535</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -19933,8 +19913,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302" t="e">
-        <v>#NUM!</v>
+      <c r="I302">
+        <v>65535</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -19962,8 +19942,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303" t="e">
-        <v>#NUM!</v>
+      <c r="E303">
+        <v>65535</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -19971,8 +19951,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303" t="e">
-        <v>#NUM!</v>
+      <c r="I303">
+        <v>65535</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -20000,8 +19980,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304" t="e">
-        <v>#NUM!</v>
+      <c r="E304">
+        <v>65535</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -20009,8 +19989,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304" t="e">
-        <v>#NUM!</v>
+      <c r="I304">
+        <v>65535</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20079,8 +20059,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306" t="e">
-        <v>#NUM!</v>
+      <c r="E306">
+        <v>65535</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20088,8 +20068,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306" t="e">
-        <v>#NUM!</v>
+      <c r="I306">
+        <v>65535</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -20117,8 +20097,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307" t="e">
-        <v>#NUM!</v>
+      <c r="E307">
+        <v>65535</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -20126,8 +20106,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307" t="e">
-        <v>#NUM!</v>
+      <c r="I307">
+        <v>65535</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -20155,8 +20135,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308" t="e">
-        <v>#NUM!</v>
+      <c r="E308">
+        <v>65535</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -20164,8 +20144,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308" t="e">
-        <v>#NUM!</v>
+      <c r="I308">
+        <v>65535</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -20193,8 +20173,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309" t="e">
-        <v>#NUM!</v>
+      <c r="E309">
+        <v>65535</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -20202,8 +20182,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309" t="e">
-        <v>#NUM!</v>
+      <c r="I309">
+        <v>65535</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -20231,8 +20211,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310" t="e">
-        <v>#NUM!</v>
+      <c r="E310">
+        <v>65535</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -20240,8 +20220,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310" t="e">
-        <v>#NUM!</v>
+      <c r="I310">
+        <v>65535</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -20269,8 +20249,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311" t="e">
-        <v>#NUM!</v>
+      <c r="E311">
+        <v>65535</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -20278,8 +20258,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311" t="e">
-        <v>#NUM!</v>
+      <c r="I311">
+        <v>65535</v>
       </c>
       <c r="J311">
         <v>0.97</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582844F7-F611-4649-957D-029AE37D5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8921BA-12E8-40D1-9CDF-9CD7931BAA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -418,21 +418,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -441,7 +441,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -449,7 +449,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -457,7 +457,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -465,21 +465,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +492,7 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +512,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5605,39 +5605,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5689,7 +5689,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5800,13 +5800,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -5815,6 +5808,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5879,11 +5879,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6396,7 +6416,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -6904,7 +6924,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -7135,7 +7155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
         <v>~TFM_INS-TS: region=POL; attribute=flo_cost;pset_pn=-IMP*Z</v>
@@ -18140,8 +18160,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257">
-        <v>65535</v>
+      <c r="E257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -18149,8 +18169,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257">
-        <v>65535</v>
+      <c r="I257" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -18178,8 +18198,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258">
-        <v>65535</v>
+      <c r="E258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -18187,8 +18207,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258">
-        <v>65535</v>
+      <c r="I258" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -18216,8 +18236,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259">
-        <v>65535</v>
+      <c r="E259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -18225,8 +18245,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259">
-        <v>65535</v>
+      <c r="I259" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -18254,8 +18274,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260">
-        <v>65535</v>
+      <c r="E260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -18263,8 +18283,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260">
-        <v>65535</v>
+      <c r="I260" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -18292,8 +18312,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261">
-        <v>65535</v>
+      <c r="E261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -18301,8 +18321,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261">
-        <v>65535</v>
+      <c r="I261" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -18330,8 +18350,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262">
-        <v>65535</v>
+      <c r="E262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -18339,8 +18359,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262">
-        <v>65535</v>
+      <c r="I262" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -18409,8 +18429,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264">
-        <v>65535</v>
+      <c r="E264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -18418,8 +18438,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264">
-        <v>65535</v>
+      <c r="I264" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -18447,8 +18467,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265">
-        <v>65535</v>
+      <c r="E265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -18456,8 +18476,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265">
-        <v>65535</v>
+      <c r="I265" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -18485,8 +18505,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266">
-        <v>65535</v>
+      <c r="E266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -18494,8 +18514,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266">
-        <v>65535</v>
+      <c r="I266" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -18523,8 +18543,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267">
-        <v>65535</v>
+      <c r="E267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -18532,8 +18552,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267">
-        <v>65535</v>
+      <c r="I267" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -18561,8 +18581,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268">
-        <v>65535</v>
+      <c r="E268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -18570,8 +18590,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268">
-        <v>65535</v>
+      <c r="I268" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -18599,8 +18619,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269">
-        <v>65535</v>
+      <c r="E269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -18608,8 +18628,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269">
-        <v>65535</v>
+      <c r="I269" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -18678,8 +18698,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271">
-        <v>65535</v>
+      <c r="E271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -18687,8 +18707,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271">
-        <v>65535</v>
+      <c r="I271" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -18716,8 +18736,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272">
-        <v>65535</v>
+      <c r="E272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -18725,8 +18745,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272">
-        <v>65535</v>
+      <c r="I272" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -18754,8 +18774,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273">
-        <v>65535</v>
+      <c r="E273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -18763,8 +18783,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273">
-        <v>65535</v>
+      <c r="I273" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -18792,8 +18812,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274">
-        <v>65535</v>
+      <c r="E274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -18801,8 +18821,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274">
-        <v>65535</v>
+      <c r="I274" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -18830,8 +18850,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275">
-        <v>65535</v>
+      <c r="E275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -18839,8 +18859,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275">
-        <v>65535</v>
+      <c r="I275" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -18868,8 +18888,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276">
-        <v>65535</v>
+      <c r="E276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -18877,8 +18897,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276">
-        <v>65535</v>
+      <c r="I276" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -19521,8 +19541,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292">
-        <v>65535</v>
+      <c r="E292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -19530,8 +19550,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292">
-        <v>65535</v>
+      <c r="I292" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -19559,8 +19579,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293">
-        <v>65535</v>
+      <c r="E293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -19568,8 +19588,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293">
-        <v>65535</v>
+      <c r="I293" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -19597,8 +19617,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294">
-        <v>65535</v>
+      <c r="E294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -19606,8 +19626,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294">
-        <v>65535</v>
+      <c r="I294" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -19635,8 +19655,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295">
-        <v>65535</v>
+      <c r="E295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -19644,8 +19664,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295">
-        <v>65535</v>
+      <c r="I295" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -19673,8 +19693,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296">
-        <v>65535</v>
+      <c r="E296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -19682,8 +19702,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296">
-        <v>65535</v>
+      <c r="I296" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -19711,8 +19731,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297">
-        <v>65535</v>
+      <c r="E297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -19720,8 +19740,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297">
-        <v>65535</v>
+      <c r="I297" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -19790,8 +19810,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299">
-        <v>65535</v>
+      <c r="E299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -19799,8 +19819,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299">
-        <v>65535</v>
+      <c r="I299" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -19828,8 +19848,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300">
-        <v>65535</v>
+      <c r="E300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -19837,8 +19857,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300">
-        <v>65535</v>
+      <c r="I300" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -19866,8 +19886,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301">
-        <v>65535</v>
+      <c r="E301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -19875,8 +19895,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301">
-        <v>65535</v>
+      <c r="I301" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -19904,8 +19924,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302">
-        <v>65535</v>
+      <c r="E302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -19913,8 +19933,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302">
-        <v>65535</v>
+      <c r="I302" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -19942,8 +19962,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303">
-        <v>65535</v>
+      <c r="E303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -19951,8 +19971,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303">
-        <v>65535</v>
+      <c r="I303" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -19980,8 +20000,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304">
-        <v>65535</v>
+      <c r="E304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -19989,8 +20009,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304">
-        <v>65535</v>
+      <c r="I304" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20059,8 +20079,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306">
-        <v>65535</v>
+      <c r="E306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20068,8 +20088,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306">
-        <v>65535</v>
+      <c r="I306" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -20097,8 +20117,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307">
-        <v>65535</v>
+      <c r="E307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -20106,8 +20126,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307">
-        <v>65535</v>
+      <c r="I307" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -20135,8 +20155,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308">
-        <v>65535</v>
+      <c r="E308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -20144,8 +20164,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308">
-        <v>65535</v>
+      <c r="I308" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -20173,8 +20193,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309">
-        <v>65535</v>
+      <c r="E309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -20182,8 +20202,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309">
-        <v>65535</v>
+      <c r="I309" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -20211,8 +20231,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310">
-        <v>65535</v>
+      <c r="E310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -20220,8 +20240,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310">
-        <v>65535</v>
+      <c r="I310" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -20249,8 +20269,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311">
-        <v>65535</v>
+      <c r="E311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -20258,8 +20278,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311">
-        <v>65535</v>
+      <c r="I311" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="J311">
         <v>0.97</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8921BA-12E8-40D1-9CDF-9CD7931BAA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69FAA33-71C1-47DD-898E-BB90FD5DC240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
@@ -418,21 +418,21 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -441,7 +441,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -449,7 +449,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -457,7 +457,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -465,21 +465,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,7 +492,7 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -512,7 +512,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -5605,39 +5605,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -5689,7 +5689,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -5800,6 +5800,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -5808,13 +5815,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -5879,31 +5879,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6416,7 +6396,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="17" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N17" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -6924,7 +6904,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="14.65" customHeight="1" thickTop="1" x14ac:dyDescent="0.45"/>
-    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:24" ht="17.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="N28" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1</f>
         <v>~TFM_INS-TS: region=POL</v>
@@ -7155,7 +7135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="2:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="5" t="str">
         <f>"~TFM_INS-TS: region="&amp;$A$1&amp;"; attribute=flo_cost;pset_pn=-IMP*Z"</f>
         <v>~TFM_INS-TS: region=POL; attribute=flo_cost;pset_pn=-IMP*Z</v>
@@ -18160,8 +18140,8 @@
       <c r="D257">
         <v>34</v>
       </c>
-      <c r="E257" t="e">
-        <v>#NUM!</v>
+      <c r="E257">
+        <v>65535</v>
       </c>
       <c r="F257">
         <v>2.42</v>
@@ -18169,8 +18149,8 @@
       <c r="H257">
         <v>1.18</v>
       </c>
-      <c r="I257" t="e">
-        <v>#NUM!</v>
+      <c r="I257">
+        <v>65535</v>
       </c>
       <c r="J257">
         <v>2.0099999999999998</v>
@@ -18198,8 +18178,8 @@
       <c r="D258">
         <v>34</v>
       </c>
-      <c r="E258" t="e">
-        <v>#NUM!</v>
+      <c r="E258">
+        <v>65535</v>
       </c>
       <c r="F258">
         <v>3.1</v>
@@ -18207,8 +18187,8 @@
       <c r="H258">
         <v>1.71</v>
       </c>
-      <c r="I258" t="e">
-        <v>#NUM!</v>
+      <c r="I258">
+        <v>65535</v>
       </c>
       <c r="J258">
         <v>2.38</v>
@@ -18236,8 +18216,8 @@
       <c r="D259">
         <v>34</v>
       </c>
-      <c r="E259" t="e">
-        <v>#NUM!</v>
+      <c r="E259">
+        <v>65535</v>
       </c>
       <c r="F259">
         <v>3.54</v>
@@ -18245,8 +18225,8 @@
       <c r="H259">
         <v>1.91</v>
       </c>
-      <c r="I259" t="e">
-        <v>#NUM!</v>
+      <c r="I259">
+        <v>65535</v>
       </c>
       <c r="J259">
         <v>2.66</v>
@@ -18274,8 +18254,8 @@
       <c r="D260">
         <v>34</v>
       </c>
-      <c r="E260" t="e">
-        <v>#NUM!</v>
+      <c r="E260">
+        <v>65535</v>
       </c>
       <c r="F260">
         <v>4.0999999999999996</v>
@@ -18283,8 +18263,8 @@
       <c r="H260">
         <v>2.27</v>
       </c>
-      <c r="I260" t="e">
-        <v>#NUM!</v>
+      <c r="I260">
+        <v>65535</v>
       </c>
       <c r="J260">
         <v>2.96</v>
@@ -18312,8 +18292,8 @@
       <c r="D261">
         <v>34</v>
       </c>
-      <c r="E261" t="e">
-        <v>#NUM!</v>
+      <c r="E261">
+        <v>65535</v>
       </c>
       <c r="F261">
         <v>3.86</v>
@@ -18321,8 +18301,8 @@
       <c r="H261">
         <v>2.54</v>
       </c>
-      <c r="I261" t="e">
-        <v>#NUM!</v>
+      <c r="I261">
+        <v>65535</v>
       </c>
       <c r="J261">
         <v>3.3</v>
@@ -18350,8 +18330,8 @@
       <c r="D262">
         <v>34</v>
       </c>
-      <c r="E262" t="e">
-        <v>#NUM!</v>
+      <c r="E262">
+        <v>65535</v>
       </c>
       <c r="F262">
         <v>3.59</v>
@@ -18359,8 +18339,8 @@
       <c r="H262">
         <v>2.73</v>
       </c>
-      <c r="I262" t="e">
-        <v>#NUM!</v>
+      <c r="I262">
+        <v>65535</v>
       </c>
       <c r="J262">
         <v>3.07</v>
@@ -18429,8 +18409,8 @@
       <c r="D264">
         <v>44</v>
       </c>
-      <c r="E264" t="e">
-        <v>#NUM!</v>
+      <c r="E264">
+        <v>65535</v>
       </c>
       <c r="F264">
         <v>1.22</v>
@@ -18438,8 +18418,8 @@
       <c r="H264">
         <v>0</v>
       </c>
-      <c r="I264" t="e">
-        <v>#NUM!</v>
+      <c r="I264">
+        <v>65535</v>
       </c>
       <c r="J264">
         <v>1.1299999999999999</v>
@@ -18467,8 +18447,8 @@
       <c r="D265">
         <v>44</v>
       </c>
-      <c r="E265" t="e">
-        <v>#NUM!</v>
+      <c r="E265">
+        <v>65535</v>
       </c>
       <c r="F265">
         <v>1.5</v>
@@ -18476,8 +18456,8 @@
       <c r="H265">
         <v>0</v>
       </c>
-      <c r="I265" t="e">
-        <v>#NUM!</v>
+      <c r="I265">
+        <v>65535</v>
       </c>
       <c r="J265">
         <v>1.31</v>
@@ -18505,8 +18485,8 @@
       <c r="D266">
         <v>44</v>
       </c>
-      <c r="E266" t="e">
-        <v>#NUM!</v>
+      <c r="E266">
+        <v>65535</v>
       </c>
       <c r="F266">
         <v>2.12</v>
@@ -18514,8 +18494,8 @@
       <c r="H266">
         <v>0</v>
       </c>
-      <c r="I266" t="e">
-        <v>#NUM!</v>
+      <c r="I266">
+        <v>65535</v>
       </c>
       <c r="J266">
         <v>1.68</v>
@@ -18543,8 +18523,8 @@
       <c r="D267">
         <v>44</v>
       </c>
-      <c r="E267" t="e">
-        <v>#NUM!</v>
+      <c r="E267">
+        <v>65535</v>
       </c>
       <c r="F267">
         <v>2.5</v>
@@ -18552,8 +18532,8 @@
       <c r="H267">
         <v>0</v>
       </c>
-      <c r="I267" t="e">
-        <v>#NUM!</v>
+      <c r="I267">
+        <v>65535</v>
       </c>
       <c r="J267">
         <v>2</v>
@@ -18581,8 +18561,8 @@
       <c r="D268">
         <v>44</v>
       </c>
-      <c r="E268" t="e">
-        <v>#NUM!</v>
+      <c r="E268">
+        <v>65535</v>
       </c>
       <c r="F268">
         <v>2.79</v>
@@ -18590,8 +18570,8 @@
       <c r="H268">
         <v>0</v>
       </c>
-      <c r="I268" t="e">
-        <v>#NUM!</v>
+      <c r="I268">
+        <v>65535</v>
       </c>
       <c r="J268">
         <v>2.08</v>
@@ -18619,8 +18599,8 @@
       <c r="D269">
         <v>44</v>
       </c>
-      <c r="E269" t="e">
-        <v>#NUM!</v>
+      <c r="E269">
+        <v>65535</v>
       </c>
       <c r="F269">
         <v>2.95</v>
@@ -18628,8 +18608,8 @@
       <c r="H269">
         <v>0</v>
       </c>
-      <c r="I269" t="e">
-        <v>#NUM!</v>
+      <c r="I269">
+        <v>65535</v>
       </c>
       <c r="J269">
         <v>2.4900000000000002</v>
@@ -18698,8 +18678,8 @@
       <c r="D271">
         <v>112</v>
       </c>
-      <c r="E271" t="e">
-        <v>#NUM!</v>
+      <c r="E271">
+        <v>65535</v>
       </c>
       <c r="F271">
         <v>1.41</v>
@@ -18707,8 +18687,8 @@
       <c r="H271">
         <v>0.98</v>
       </c>
-      <c r="I271" t="e">
-        <v>#NUM!</v>
+      <c r="I271">
+        <v>65535</v>
       </c>
       <c r="J271">
         <v>1.23</v>
@@ -18736,8 +18716,8 @@
       <c r="D272">
         <v>112</v>
       </c>
-      <c r="E272" t="e">
-        <v>#NUM!</v>
+      <c r="E272">
+        <v>65535</v>
       </c>
       <c r="F272">
         <v>2.04</v>
@@ -18745,8 +18725,8 @@
       <c r="H272">
         <v>1.05</v>
       </c>
-      <c r="I272" t="e">
-        <v>#NUM!</v>
+      <c r="I272">
+        <v>65535</v>
       </c>
       <c r="J272">
         <v>1.52</v>
@@ -18774,8 +18754,8 @@
       <c r="D273">
         <v>112</v>
       </c>
-      <c r="E273" t="e">
-        <v>#NUM!</v>
+      <c r="E273">
+        <v>65535</v>
       </c>
       <c r="F273">
         <v>2.4</v>
@@ -18783,8 +18763,8 @@
       <c r="H273">
         <v>1.05</v>
       </c>
-      <c r="I273" t="e">
-        <v>#NUM!</v>
+      <c r="I273">
+        <v>65535</v>
       </c>
       <c r="J273">
         <v>1.71</v>
@@ -18812,8 +18792,8 @@
       <c r="D274">
         <v>112</v>
       </c>
-      <c r="E274" t="e">
-        <v>#NUM!</v>
+      <c r="E274">
+        <v>65535</v>
       </c>
       <c r="F274">
         <v>2.6</v>
@@ -18821,8 +18801,8 @@
       <c r="H274">
         <v>1.06</v>
       </c>
-      <c r="I274" t="e">
-        <v>#NUM!</v>
+      <c r="I274">
+        <v>65535</v>
       </c>
       <c r="J274">
         <v>1.85</v>
@@ -18850,8 +18830,8 @@
       <c r="D275">
         <v>112</v>
       </c>
-      <c r="E275" t="e">
-        <v>#NUM!</v>
+      <c r="E275">
+        <v>65535</v>
       </c>
       <c r="F275">
         <v>2.85</v>
@@ -18859,8 +18839,8 @@
       <c r="H275">
         <v>1.08</v>
       </c>
-      <c r="I275" t="e">
-        <v>#NUM!</v>
+      <c r="I275">
+        <v>65535</v>
       </c>
       <c r="J275">
         <v>2</v>
@@ -18888,8 +18868,8 @@
       <c r="D276">
         <v>112</v>
       </c>
-      <c r="E276" t="e">
-        <v>#NUM!</v>
+      <c r="E276">
+        <v>65535</v>
       </c>
       <c r="F276">
         <v>2.97</v>
@@ -18897,8 +18877,8 @@
       <c r="H276">
         <v>0</v>
       </c>
-      <c r="I276" t="e">
-        <v>#NUM!</v>
+      <c r="I276">
+        <v>65535</v>
       </c>
       <c r="J276">
         <v>2.15</v>
@@ -19541,8 +19521,8 @@
       <c r="D292">
         <v>50</v>
       </c>
-      <c r="E292" t="e">
-        <v>#NUM!</v>
+      <c r="E292">
+        <v>65535</v>
       </c>
       <c r="F292">
         <v>1.1000000000000001</v>
@@ -19550,8 +19530,8 @@
       <c r="H292">
         <v>-4.33</v>
       </c>
-      <c r="I292" t="e">
-        <v>#NUM!</v>
+      <c r="I292">
+        <v>65535</v>
       </c>
       <c r="J292">
         <v>0.81</v>
@@ -19579,8 +19559,8 @@
       <c r="D293">
         <v>50</v>
       </c>
-      <c r="E293" t="e">
-        <v>#NUM!</v>
+      <c r="E293">
+        <v>65535</v>
       </c>
       <c r="F293">
         <v>1.77</v>
@@ -19588,8 +19568,8 @@
       <c r="H293">
         <v>-6.1</v>
       </c>
-      <c r="I293" t="e">
-        <v>#NUM!</v>
+      <c r="I293">
+        <v>65535</v>
       </c>
       <c r="J293">
         <v>1.27</v>
@@ -19617,8 +19597,8 @@
       <c r="D294">
         <v>50</v>
       </c>
-      <c r="E294" t="e">
-        <v>#NUM!</v>
+      <c r="E294">
+        <v>65535</v>
       </c>
       <c r="F294">
         <v>1.87</v>
@@ -19626,8 +19606,8 @@
       <c r="H294">
         <v>-6.86</v>
       </c>
-      <c r="I294" t="e">
-        <v>#NUM!</v>
+      <c r="I294">
+        <v>65535</v>
       </c>
       <c r="J294">
         <v>1.1499999999999999</v>
@@ -19655,8 +19635,8 @@
       <c r="D295">
         <v>50</v>
       </c>
-      <c r="E295" t="e">
-        <v>#NUM!</v>
+      <c r="E295">
+        <v>65535</v>
       </c>
       <c r="F295">
         <v>1.96</v>
@@ -19664,8 +19644,8 @@
       <c r="H295">
         <v>-9.2100000000000009</v>
       </c>
-      <c r="I295" t="e">
-        <v>#NUM!</v>
+      <c r="I295">
+        <v>65535</v>
       </c>
       <c r="J295">
         <v>1.31</v>
@@ -19693,8 +19673,8 @@
       <c r="D296">
         <v>50</v>
       </c>
-      <c r="E296" t="e">
-        <v>#NUM!</v>
+      <c r="E296">
+        <v>65535</v>
       </c>
       <c r="F296">
         <v>2.13</v>
@@ -19702,8 +19682,8 @@
       <c r="H296">
         <v>-6.95</v>
       </c>
-      <c r="I296" t="e">
-        <v>#NUM!</v>
+      <c r="I296">
+        <v>65535</v>
       </c>
       <c r="J296">
         <v>1.6</v>
@@ -19731,8 +19711,8 @@
       <c r="D297">
         <v>50</v>
       </c>
-      <c r="E297" t="e">
-        <v>#NUM!</v>
+      <c r="E297">
+        <v>65535</v>
       </c>
       <c r="F297">
         <v>2</v>
@@ -19740,8 +19720,8 @@
       <c r="H297">
         <v>-10.07</v>
       </c>
-      <c r="I297" t="e">
-        <v>#NUM!</v>
+      <c r="I297">
+        <v>65535</v>
       </c>
       <c r="J297">
         <v>1.55</v>
@@ -19810,8 +19790,8 @@
       <c r="D299">
         <v>52</v>
       </c>
-      <c r="E299" t="e">
-        <v>#NUM!</v>
+      <c r="E299">
+        <v>65535</v>
       </c>
       <c r="F299">
         <v>0.61</v>
@@ -19819,8 +19799,8 @@
       <c r="H299">
         <v>0</v>
       </c>
-      <c r="I299" t="e">
-        <v>#NUM!</v>
+      <c r="I299">
+        <v>65535</v>
       </c>
       <c r="J299">
         <v>0.53</v>
@@ -19848,8 +19828,8 @@
       <c r="D300">
         <v>63</v>
       </c>
-      <c r="E300" t="e">
-        <v>#NUM!</v>
+      <c r="E300">
+        <v>65535</v>
       </c>
       <c r="F300">
         <v>1.07</v>
@@ -19857,8 +19837,8 @@
       <c r="H300">
         <v>0</v>
       </c>
-      <c r="I300" t="e">
-        <v>#NUM!</v>
+      <c r="I300">
+        <v>65535</v>
       </c>
       <c r="J300">
         <v>0.6</v>
@@ -19886,8 +19866,8 @@
       <c r="D301">
         <v>52</v>
       </c>
-      <c r="E301" t="e">
-        <v>#NUM!</v>
+      <c r="E301">
+        <v>65535</v>
       </c>
       <c r="F301">
         <v>1.0900000000000001</v>
@@ -19895,8 +19875,8 @@
       <c r="H301">
         <v>0</v>
       </c>
-      <c r="I301" t="e">
-        <v>#NUM!</v>
+      <c r="I301">
+        <v>65535</v>
       </c>
       <c r="J301">
         <v>0.6</v>
@@ -19924,8 +19904,8 @@
       <c r="D302">
         <v>63</v>
       </c>
-      <c r="E302" t="e">
-        <v>#NUM!</v>
+      <c r="E302">
+        <v>65535</v>
       </c>
       <c r="F302">
         <v>1.25</v>
@@ -19933,8 +19913,8 @@
       <c r="H302">
         <v>0</v>
       </c>
-      <c r="I302" t="e">
-        <v>#NUM!</v>
+      <c r="I302">
+        <v>65535</v>
       </c>
       <c r="J302">
         <v>0.87</v>
@@ -19962,8 +19942,8 @@
       <c r="D303">
         <v>52</v>
       </c>
-      <c r="E303" t="e">
-        <v>#NUM!</v>
+      <c r="E303">
+        <v>65535</v>
       </c>
       <c r="F303">
         <v>1.35</v>
@@ -19971,8 +19951,8 @@
       <c r="H303">
         <v>0</v>
       </c>
-      <c r="I303" t="e">
-        <v>#NUM!</v>
+      <c r="I303">
+        <v>65535</v>
       </c>
       <c r="J303">
         <v>0.78</v>
@@ -20000,8 +19980,8 @@
       <c r="D304">
         <v>63</v>
       </c>
-      <c r="E304" t="e">
-        <v>#NUM!</v>
+      <c r="E304">
+        <v>65535</v>
       </c>
       <c r="F304">
         <v>1.62</v>
@@ -20009,8 +19989,8 @@
       <c r="H304">
         <v>-2.31</v>
       </c>
-      <c r="I304" t="e">
-        <v>#NUM!</v>
+      <c r="I304">
+        <v>65535</v>
       </c>
       <c r="J304">
         <v>0.61</v>
@@ -20079,8 +20059,8 @@
       <c r="D306">
         <v>163</v>
       </c>
-      <c r="E306" t="e">
-        <v>#NUM!</v>
+      <c r="E306">
+        <v>65535</v>
       </c>
       <c r="F306">
         <v>0.75</v>
@@ -20088,8 +20068,8 @@
       <c r="H306">
         <v>0.46</v>
       </c>
-      <c r="I306" t="e">
-        <v>#NUM!</v>
+      <c r="I306">
+        <v>65535</v>
       </c>
       <c r="J306">
         <v>0.54</v>
@@ -20117,8 +20097,8 @@
       <c r="D307">
         <v>166</v>
       </c>
-      <c r="E307" t="e">
-        <v>#NUM!</v>
+      <c r="E307">
+        <v>65535</v>
       </c>
       <c r="F307">
         <v>1.1499999999999999</v>
@@ -20126,8 +20106,8 @@
       <c r="H307">
         <v>0.51</v>
       </c>
-      <c r="I307" t="e">
-        <v>#NUM!</v>
+      <c r="I307">
+        <v>65535</v>
       </c>
       <c r="J307">
         <v>0.74</v>
@@ -20155,8 +20135,8 @@
       <c r="D308">
         <v>163</v>
       </c>
-      <c r="E308" t="e">
-        <v>#NUM!</v>
+      <c r="E308">
+        <v>65535</v>
       </c>
       <c r="F308">
         <v>1.21</v>
@@ -20164,8 +20144,8 @@
       <c r="H308">
         <v>-0.95</v>
       </c>
-      <c r="I308" t="e">
-        <v>#NUM!</v>
+      <c r="I308">
+        <v>65535</v>
       </c>
       <c r="J308">
         <v>0.88</v>
@@ -20193,8 +20173,8 @@
       <c r="D309">
         <v>166</v>
       </c>
-      <c r="E309" t="e">
-        <v>#NUM!</v>
+      <c r="E309">
+        <v>65535</v>
       </c>
       <c r="F309">
         <v>1.28</v>
@@ -20202,8 +20182,8 @@
       <c r="H309">
         <v>-1.8</v>
       </c>
-      <c r="I309" t="e">
-        <v>#NUM!</v>
+      <c r="I309">
+        <v>65535</v>
       </c>
       <c r="J309">
         <v>0.89</v>
@@ -20231,8 +20211,8 @@
       <c r="D310">
         <v>163</v>
       </c>
-      <c r="E310" t="e">
-        <v>#NUM!</v>
+      <c r="E310">
+        <v>65535</v>
       </c>
       <c r="F310">
         <v>1.48</v>
@@ -20240,8 +20220,8 @@
       <c r="H310">
         <v>-5.93</v>
       </c>
-      <c r="I310" t="e">
-        <v>#NUM!</v>
+      <c r="I310">
+        <v>65535</v>
       </c>
       <c r="J310">
         <v>1.08</v>
@@ -20269,8 +20249,8 @@
       <c r="D311">
         <v>166</v>
       </c>
-      <c r="E311" t="e">
-        <v>#NUM!</v>
+      <c r="E311">
+        <v>65535</v>
       </c>
       <c r="F311">
         <v>1.59</v>
@@ -20278,8 +20258,8 @@
       <c r="H311">
         <v>-5.35</v>
       </c>
-      <c r="I311" t="e">
-        <v>#NUM!</v>
+      <c r="I311">
+        <v>65535</v>
       </c>
       <c r="J311">
         <v>0.97</v>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E69FAA33-71C1-47DD-898E-BB90FD5DC240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0019011-EC84-47FA-805F-23F97E2B8670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_POL_grids_kan50/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0019011-EC84-47FA-805F-23F97E2B8670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F5D64F-AC29-4464-B5C0-2890C60DE783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
